--- a/Dowling/dowling-vs-valley-offense.xlsx
+++ b/Dowling/dowling-vs-valley-offense.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Rf1a532f04fbf4179"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Rfd3d36a8940c448e"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -170,6 +185,9 @@
   </si>
   <si>
     <t>ARIZONA</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
   <si>
     <t>ICE Q MIRROR BULLDOGS</t>
@@ -278,7 +296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X121"/>
+  <dimension ref="A1:AC121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -353,6 +371,21 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -362,7 +395,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -371,13 +404,13 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -388,7 +421,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -397,13 +430,13 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -414,7 +447,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -423,13 +456,13 @@
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -440,7 +473,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -449,13 +482,13 @@
         <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -466,7 +499,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -475,13 +508,13 @@
         <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -492,7 +525,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -501,13 +534,13 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -518,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -527,13 +560,13 @@
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -544,7 +577,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -553,13 +586,13 @@
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -570,7 +603,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -579,25 +612,25 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10" t="s">
-        <v>40</v>
-      </c>
-      <c r="S10" t="s">
-        <v>41</v>
-      </c>
-      <c r="T10" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="X10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -608,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -617,25 +650,25 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
-      </c>
-      <c r="S11" t="s">
-        <v>43</v>
-      </c>
-      <c r="T11" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="X11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -646,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -655,25 +688,25 @@
         <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J12">
         <v>6</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
-      </c>
-      <c r="S12" t="s">
         <v>45</v>
       </c>
-      <c r="T12" t="s">
-        <v>46</v>
+      <c r="X12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -684,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -693,25 +726,25 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>40</v>
-      </c>
-      <c r="S13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T13" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="X13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -722,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -731,25 +764,25 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>49</v>
-      </c>
-      <c r="S14" t="s">
-        <v>50</v>
-      </c>
-      <c r="T14" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="X14" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -760,7 +793,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -769,10 +802,10 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
-      </c>
-      <c r="S15" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="X15" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="16">
@@ -783,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -792,28 +825,31 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>49</v>
-      </c>
-      <c r="S16" t="s">
-        <v>52</v>
-      </c>
-      <c r="T16" t="s">
-        <v>53</v>
-      </c>
-      <c r="V16" t="s">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="P16" t="s">
+        <v>58</v>
+      </c>
+      <c r="X16" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -824,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -833,13 +869,13 @@
         <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -850,7 +886,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -859,13 +895,13 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -876,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -885,13 +921,13 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -902,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -911,13 +947,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -928,7 +964,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -937,13 +973,13 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -954,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -963,13 +999,13 @@
         <v>6</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -980,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -989,25 +1025,25 @@
         <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J23">
         <v>28</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
-      </c>
-      <c r="S23" t="s">
         <v>45</v>
       </c>
-      <c r="T23" t="s">
-        <v>55</v>
+      <c r="X23" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="24">
@@ -1018,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1027,25 +1063,28 @@
         <v>10</v>
       </c>
       <c r="G24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24" t="s">
+        <v>54</v>
+      </c>
+      <c r="P24" t="s">
         <v>29</v>
       </c>
-      <c r="H24" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24">
-        <v>2</v>
-      </c>
-      <c r="K24" t="s">
-        <v>49</v>
-      </c>
-      <c r="S24" t="s">
-        <v>52</v>
-      </c>
-      <c r="T24" t="s">
-        <v>56</v>
+      <c r="X24" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -1056,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1065,25 +1104,25 @@
         <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25" t="s">
-        <v>40</v>
-      </c>
-      <c r="S25" t="s">
-        <v>41</v>
-      </c>
-      <c r="T25" t="s">
-        <v>57</v>
+        <v>45</v>
+      </c>
+      <c r="X25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="26">
@@ -1094,7 +1133,7 @@
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -1103,25 +1142,25 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I26" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J26">
         <v>3</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
-      </c>
-      <c r="S26" t="s">
-        <v>47</v>
-      </c>
-      <c r="T26" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="X26" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="27">
@@ -1132,7 +1171,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1141,25 +1180,25 @@
         <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I27" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>49</v>
-      </c>
-      <c r="S27" t="s">
-        <v>43</v>
-      </c>
-      <c r="T27" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="X27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="28">
@@ -1170,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1179,27 +1218,27 @@
         <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J28">
         <v>3</v>
       </c>
       <c r="K28" t="s">
-        <v>49</v>
-      </c>
-      <c r="S28" t="s">
-        <v>50</v>
-      </c>
-      <c r="T28" t="s">
-        <v>61</v>
-      </c>
-      <c r="W28">
+        <v>54</v>
+      </c>
+      <c r="X28" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1211,7 +1250,7 @@
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1220,18 +1259,18 @@
         <v>7</v>
       </c>
       <c r="G29" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>49</v>
-      </c>
-      <c r="S29" t="s">
-        <v>62</v>
-      </c>
-      <c r="W29">
+        <v>54</v>
+      </c>
+      <c r="X29" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1243,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -1252,15 +1291,15 @@
         <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H30" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I30" t="s">
-        <v>64</v>
-      </c>
-      <c r="W30">
+        <v>70</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1272,7 +1311,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1281,13 +1320,13 @@
         <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I31" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
@@ -1298,7 +1337,7 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -1307,13 +1346,13 @@
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H32" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I32" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33">
@@ -1324,7 +1363,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -1333,13 +1372,13 @@
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I33" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34">
@@ -1350,7 +1389,7 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1359,13 +1398,13 @@
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H34" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I34" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1376,7 +1415,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1385,25 +1424,25 @@
         <v>10</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H35" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J35">
         <v>11</v>
       </c>
       <c r="K35" t="s">
-        <v>40</v>
-      </c>
-      <c r="S35" t="s">
         <v>45</v>
       </c>
-      <c r="T35" t="s">
-        <v>65</v>
+      <c r="X35" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="36">
@@ -1414,7 +1453,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1423,28 +1462,28 @@
         <v>10</v>
       </c>
       <c r="G36" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J36">
         <v>6</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
-      </c>
-      <c r="S36" t="s">
-        <v>43</v>
-      </c>
-      <c r="T36" t="s">
-        <v>42</v>
-      </c>
-      <c r="V36" t="s">
-        <v>39</v>
+        <v>45</v>
+      </c>
+      <c r="X36" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -1455,7 +1494,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -1464,25 +1503,25 @@
         <v>6</v>
       </c>
       <c r="G37" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H37" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I37" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J37">
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>49</v>
-      </c>
-      <c r="S37" t="s">
-        <v>45</v>
-      </c>
-      <c r="T37" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="X37" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1532,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -1502,25 +1541,28 @@
         <v>4</v>
       </c>
       <c r="G38" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H38" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I38" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J38">
         <v>4</v>
       </c>
       <c r="K38" t="s">
-        <v>49</v>
-      </c>
-      <c r="S38" t="s">
-        <v>52</v>
-      </c>
-      <c r="T38" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="P38" t="s">
+        <v>29</v>
+      </c>
+      <c r="X38" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="39">
@@ -1531,7 +1573,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1540,13 +1582,13 @@
         <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H39" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -1557,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -1566,13 +1608,13 @@
         <v>8</v>
       </c>
       <c r="G40" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41">
@@ -1583,7 +1625,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -1592,13 +1634,13 @@
         <v>10</v>
       </c>
       <c r="G41" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H41" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I41" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42">
@@ -1609,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1618,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="G42" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H42" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I42" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -1635,7 +1677,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1644,25 +1686,25 @@
         <v>10</v>
       </c>
       <c r="G43" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" t="s">
+        <v>37</v>
+      </c>
+      <c r="I43" t="s">
         <v>39</v>
-      </c>
-      <c r="H43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" t="s">
-        <v>34</v>
       </c>
       <c r="J43">
         <v>6</v>
       </c>
       <c r="K43" t="s">
-        <v>40</v>
-      </c>
-      <c r="S43" t="s">
         <v>45</v>
       </c>
-      <c r="T43" t="s">
-        <v>69</v>
+      <c r="X43" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="44">
@@ -1673,7 +1715,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -1682,25 +1724,25 @@
         <v>4</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I44" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>49</v>
-      </c>
-      <c r="S44" t="s">
-        <v>41</v>
-      </c>
-      <c r="T44" t="s">
-        <v>70</v>
+        <v>54</v>
+      </c>
+      <c r="X44" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="45">
@@ -1711,7 +1753,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -1720,28 +1762,28 @@
         <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I45" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J45">
         <v>53</v>
       </c>
       <c r="K45" t="s">
-        <v>40</v>
-      </c>
-      <c r="S45" t="s">
-        <v>62</v>
-      </c>
-      <c r="T45" t="s">
-        <v>72</v>
-      </c>
-      <c r="V45" t="s">
-        <v>39</v>
+        <v>45</v>
+      </c>
+      <c r="X45" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -1752,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1764,13 +1806,13 @@
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H46" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47">
@@ -1781,7 +1823,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1790,13 +1832,13 @@
         <v>10</v>
       </c>
       <c r="G47" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H47" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I47" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
@@ -1807,7 +1849,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1816,13 +1858,13 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H48" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49">
@@ -1833,7 +1875,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1842,13 +1884,13 @@
         <v>12</v>
       </c>
       <c r="G49" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H49" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I49" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50">
@@ -1859,7 +1901,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -1868,13 +1910,13 @@
         <v>12</v>
       </c>
       <c r="G50" t="s">
+        <v>44</v>
+      </c>
+      <c r="H50" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" t="s">
         <v>39</v>
-      </c>
-      <c r="H50" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="51">
@@ -1885,7 +1927,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -1894,13 +1936,13 @@
         <v>5</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I51" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52">
@@ -1911,7 +1953,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1920,25 +1962,25 @@
         <v>10</v>
       </c>
       <c r="G52" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H52" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I52" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J52">
         <v>3</v>
       </c>
       <c r="K52" t="s">
-        <v>49</v>
-      </c>
-      <c r="S52" t="s">
-        <v>75</v>
-      </c>
-      <c r="T52" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="X52" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="53">
@@ -1949,7 +1991,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -1958,25 +2000,25 @@
         <v>7</v>
       </c>
       <c r="G53" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H53" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J53">
         <v>3</v>
       </c>
       <c r="K53" t="s">
-        <v>49</v>
-      </c>
-      <c r="S53" t="s">
-        <v>41</v>
-      </c>
-      <c r="T53" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="X53" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="54">
@@ -1987,7 +2029,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D54">
         <v>3</v>
@@ -1996,25 +2038,25 @@
         <v>5</v>
       </c>
       <c r="G54" t="s">
+        <v>44</v>
+      </c>
+      <c r="H54" t="s">
+        <v>37</v>
+      </c>
+      <c r="I54" t="s">
         <v>39</v>
-      </c>
-      <c r="H54" t="s">
-        <v>32</v>
-      </c>
-      <c r="I54" t="s">
-        <v>34</v>
       </c>
       <c r="J54">
         <v>11</v>
       </c>
       <c r="K54" t="s">
-        <v>40</v>
-      </c>
-      <c r="S54" t="s">
-        <v>62</v>
-      </c>
-      <c r="T54" t="s">
-        <v>76</v>
+        <v>45</v>
+      </c>
+      <c r="X54" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="55">
@@ -2025,7 +2067,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2034,25 +2076,25 @@
         <v>10</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H55" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I55" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J55">
         <v>42</v>
       </c>
       <c r="K55" t="s">
-        <v>40</v>
-      </c>
-      <c r="S55" t="s">
-        <v>41</v>
-      </c>
-      <c r="T55" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+      <c r="X55" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="56">
@@ -2063,7 +2105,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2072,25 +2114,25 @@
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J56">
         <v>3</v>
       </c>
       <c r="K56" t="s">
-        <v>40</v>
-      </c>
-      <c r="S56" t="s">
         <v>45</v>
       </c>
-      <c r="T56" t="s">
-        <v>69</v>
+      <c r="X56" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="57">
@@ -2101,7 +2143,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2113,13 +2155,13 @@
         <v>3</v>
       </c>
       <c r="G57" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H57" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I57" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58">
@@ -2130,7 +2172,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2139,7 +2181,7 @@
         <v>10</v>
       </c>
       <c r="G58" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
@@ -2150,7 +2192,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2159,13 +2201,13 @@
         <v>10</v>
       </c>
       <c r="G59" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H59" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I59" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
@@ -2176,7 +2218,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2185,13 +2227,13 @@
         <v>10</v>
       </c>
       <c r="G60" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H60" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
@@ -2202,7 +2244,7 @@
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2211,13 +2253,13 @@
         <v>10</v>
       </c>
       <c r="G61" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H61" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I61" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62">
@@ -2228,7 +2270,7 @@
         <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2237,25 +2279,25 @@
         <v>10</v>
       </c>
       <c r="G62" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H62" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J62">
         <v>9</v>
       </c>
       <c r="K62" t="s">
-        <v>40</v>
-      </c>
-      <c r="S62" t="s">
-        <v>41</v>
-      </c>
-      <c r="T62" t="s">
-        <v>69</v>
+        <v>45</v>
+      </c>
+      <c r="X62" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="63">
@@ -2266,7 +2308,7 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2275,25 +2317,25 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H63" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>49</v>
-      </c>
-      <c r="S63" t="s">
-        <v>41</v>
-      </c>
-      <c r="T63" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="X63" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="64">
@@ -2304,7 +2346,7 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2313,22 +2355,22 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H64" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J64">
         <v>2</v>
       </c>
       <c r="K64" t="s">
-        <v>40</v>
-      </c>
-      <c r="T64" t="s">
-        <v>80</v>
+        <v>45</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="65">
@@ -2339,7 +2381,7 @@
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2348,25 +2390,25 @@
         <v>10</v>
       </c>
       <c r="G65" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H65" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J65">
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>40</v>
-      </c>
-      <c r="S65" t="s">
         <v>45</v>
       </c>
-      <c r="T65" t="s">
-        <v>44</v>
+      <c r="X65" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="66">
@@ -2377,7 +2419,7 @@
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -2386,25 +2428,25 @@
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H66" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J66">
         <v>3</v>
       </c>
       <c r="K66" t="s">
-        <v>40</v>
-      </c>
-      <c r="S66" t="s">
-        <v>41</v>
-      </c>
-      <c r="T66" t="s">
-        <v>69</v>
+        <v>45</v>
+      </c>
+      <c r="X66" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="67">
@@ -2415,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D67">
         <v>3</v>
@@ -2424,25 +2466,25 @@
         <v>3</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J67">
         <v>2</v>
       </c>
       <c r="K67" t="s">
-        <v>49</v>
-      </c>
-      <c r="S67" t="s">
-        <v>47</v>
-      </c>
-      <c r="T67" t="s">
-        <v>58</v>
+        <v>54</v>
+      </c>
+      <c r="X67" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="68">
@@ -2453,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -2462,7 +2504,7 @@
         <v>3</v>
       </c>
       <c r="G68" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69">
@@ -2473,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D69">
         <v>4</v>
@@ -2482,13 +2524,13 @@
         <v>7</v>
       </c>
       <c r="G69" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H69" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I69" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70">
@@ -2499,7 +2541,7 @@
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2508,13 +2550,13 @@
         <v>10</v>
       </c>
       <c r="G70" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71">
@@ -2525,7 +2567,7 @@
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -2534,13 +2576,13 @@
         <v>9</v>
       </c>
       <c r="G71" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H71" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72">
@@ -2551,7 +2593,7 @@
         <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2560,13 +2602,13 @@
         <v>10</v>
       </c>
       <c r="G72" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H72" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73">
@@ -2577,7 +2619,7 @@
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -2586,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="G73" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H73" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74">
@@ -2603,7 +2645,7 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -2612,13 +2654,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H74" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I74" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -2629,7 +2671,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D75">
         <v>4</v>
@@ -2638,13 +2680,13 @@
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H75" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I75" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76">
@@ -2655,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2664,25 +2706,25 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H76" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J76">
         <v>6</v>
       </c>
       <c r="K76" t="s">
-        <v>40</v>
-      </c>
-      <c r="S76" t="s">
-        <v>41</v>
-      </c>
-      <c r="T76" t="s">
-        <v>69</v>
+        <v>45</v>
+      </c>
+      <c r="X76" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -2693,7 +2735,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D77">
         <v>2</v>
@@ -2702,25 +2744,25 @@
         <v>4</v>
       </c>
       <c r="G77" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H77" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>49</v>
-      </c>
-      <c r="S77" t="s">
-        <v>41</v>
-      </c>
-      <c r="T77" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="X77" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="78">
@@ -2731,7 +2773,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D78">
         <v>3</v>
@@ -2740,25 +2782,25 @@
         <v>4</v>
       </c>
       <c r="G78" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H78" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I78" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J78">
         <v>30</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
-      </c>
-      <c r="S78" t="s">
-        <v>41</v>
-      </c>
-      <c r="T78" t="s">
-        <v>81</v>
+        <v>45</v>
+      </c>
+      <c r="X78" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="79">
@@ -2769,7 +2811,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -2778,25 +2820,25 @@
         <v>10</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H79" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J79">
         <v>7</v>
       </c>
       <c r="K79" t="s">
-        <v>40</v>
-      </c>
-      <c r="S79" t="s">
         <v>45</v>
       </c>
-      <c r="T79" t="s">
-        <v>44</v>
+      <c r="X79" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="80">
@@ -2807,7 +2849,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -2816,25 +2858,25 @@
         <v>3</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H80" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J80">
         <v>4</v>
       </c>
       <c r="K80" t="s">
-        <v>40</v>
-      </c>
-      <c r="S80" t="s">
-        <v>41</v>
-      </c>
-      <c r="T80" t="s">
-        <v>69</v>
+        <v>45</v>
+      </c>
+      <c r="X80" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="81">
@@ -2845,7 +2887,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2854,25 +2896,25 @@
         <v>10</v>
       </c>
       <c r="G81" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H81" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J81">
         <v>5</v>
       </c>
       <c r="K81" t="s">
-        <v>40</v>
-      </c>
-      <c r="S81" t="s">
         <v>45</v>
       </c>
-      <c r="T81" t="s">
-        <v>44</v>
+      <c r="X81" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="82">
@@ -2883,7 +2925,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -2892,25 +2934,25 @@
         <v>5</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H82" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J82">
         <v>3</v>
       </c>
       <c r="K82" t="s">
-        <v>40</v>
-      </c>
-      <c r="S82" t="s">
-        <v>41</v>
-      </c>
-      <c r="T82" t="s">
-        <v>69</v>
+        <v>45</v>
+      </c>
+      <c r="X82" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="83">
@@ -2921,7 +2963,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -2930,25 +2972,25 @@
         <v>4</v>
       </c>
       <c r="G83" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J83">
         <v>9</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
-      </c>
-      <c r="S83" t="s">
         <v>45</v>
       </c>
-      <c r="T83" t="s">
-        <v>44</v>
+      <c r="X83" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="84">
@@ -2959,7 +3001,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2968,22 +3010,22 @@
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H84" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J84">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
-      </c>
-      <c r="T84" t="s">
-        <v>80</v>
+        <v>45</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="85">
@@ -2994,7 +3036,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3006,13 +3048,13 @@
         <v>3</v>
       </c>
       <c r="G85" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H85" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I85" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86">
@@ -3023,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3032,13 +3074,13 @@
         <v>10</v>
       </c>
       <c r="G86" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H86" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
@@ -3049,7 +3091,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3058,13 +3100,13 @@
         <v>10</v>
       </c>
       <c r="G87" t="s">
+        <v>44</v>
+      </c>
+      <c r="H87" t="s">
+        <v>37</v>
+      </c>
+      <c r="I87" t="s">
         <v>39</v>
-      </c>
-      <c r="H87" t="s">
-        <v>32</v>
-      </c>
-      <c r="I87" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="88">
@@ -3075,7 +3117,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3084,13 +3126,13 @@
         <v>10</v>
       </c>
       <c r="G88" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H88" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -3101,7 +3143,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -3110,13 +3152,13 @@
         <v>7</v>
       </c>
       <c r="G89" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H89" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90">
@@ -3127,7 +3169,7 @@
         <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -3136,13 +3178,13 @@
         <v>7</v>
       </c>
       <c r="G90" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H90" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I90" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91">
@@ -3153,7 +3195,7 @@
         <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D91">
         <v>4</v>
@@ -3162,13 +3204,13 @@
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H91" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I91" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92">
@@ -3179,7 +3221,7 @@
         <v>4</v>
       </c>
       <c r="C92" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3188,25 +3230,25 @@
         <v>10</v>
       </c>
       <c r="G92" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H92" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I92" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J92">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>49</v>
-      </c>
-      <c r="S92" t="s">
-        <v>45</v>
-      </c>
-      <c r="T92" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="X92" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="93">
@@ -3217,7 +3259,7 @@
         <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -3226,25 +3268,25 @@
         <v>9</v>
       </c>
       <c r="G93" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H93" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J93">
         <v>4</v>
       </c>
       <c r="K93" t="s">
-        <v>49</v>
-      </c>
-      <c r="S93" t="s">
-        <v>45</v>
-      </c>
-      <c r="T93" t="s">
-        <v>82</v>
+        <v>54</v>
+      </c>
+      <c r="X93" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="94">
@@ -3255,7 +3297,7 @@
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -3264,28 +3306,28 @@
         <v>6</v>
       </c>
       <c r="G94" t="s">
+        <v>44</v>
+      </c>
+      <c r="H94" t="s">
+        <v>37</v>
+      </c>
+      <c r="I94" t="s">
         <v>39</v>
       </c>
-      <c r="H94" t="s">
-        <v>32</v>
-      </c>
-      <c r="I94" t="s">
-        <v>34</v>
-      </c>
       <c r="J94">
         <v>10</v>
       </c>
       <c r="K94" t="s">
-        <v>40</v>
-      </c>
-      <c r="S94" t="s">
-        <v>83</v>
-      </c>
-      <c r="T94" t="s">
-        <v>84</v>
-      </c>
-      <c r="V94" t="s">
-        <v>39</v>
+        <v>45</v>
+      </c>
+      <c r="X94" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="95">
@@ -3296,7 +3338,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3305,25 +3347,25 @@
         <v>8</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H95" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I95" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J95">
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>49</v>
-      </c>
-      <c r="S95" t="s">
-        <v>41</v>
-      </c>
-      <c r="T95" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="X95" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="96">
@@ -3334,7 +3376,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -3343,25 +3385,25 @@
         <v>8</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H96" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I96" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>49</v>
-      </c>
-      <c r="S96" t="s">
-        <v>50</v>
-      </c>
-      <c r="T96" t="s">
-        <v>61</v>
+        <v>54</v>
+      </c>
+      <c r="X96" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="97">
@@ -3372,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -3381,25 +3423,25 @@
         <v>10</v>
       </c>
       <c r="G97" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H97" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I97" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>49</v>
-      </c>
-      <c r="S97" t="s">
-        <v>41</v>
-      </c>
-      <c r="T97" t="s">
-        <v>85</v>
+        <v>54</v>
+      </c>
+      <c r="X97" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="98">
@@ -3410,7 +3452,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D98">
         <v>4</v>
@@ -3419,13 +3461,13 @@
         <v>10</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H98" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I98" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99">
@@ -3436,7 +3478,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3445,13 +3487,13 @@
         <v>10</v>
       </c>
       <c r="G99" t="s">
+        <v>44</v>
+      </c>
+      <c r="H99" t="s">
+        <v>37</v>
+      </c>
+      <c r="I99" t="s">
         <v>39</v>
-      </c>
-      <c r="H99" t="s">
-        <v>32</v>
-      </c>
-      <c r="I99" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="100">
@@ -3462,7 +3504,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -3471,13 +3513,13 @@
         <v>5</v>
       </c>
       <c r="G100" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H100" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I100" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101">
@@ -3488,7 +3530,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>3</v>
@@ -3497,13 +3539,13 @@
         <v>2</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H101" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I101" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102">
@@ -3514,7 +3556,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3523,13 +3565,13 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H102" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I102" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="103">
@@ -3540,7 +3582,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -3549,13 +3591,13 @@
         <v>10</v>
       </c>
       <c r="G103" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H103" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I103" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104">
@@ -3566,7 +3608,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D104">
         <v>3</v>
@@ -3575,13 +3617,13 @@
         <v>5</v>
       </c>
       <c r="G104" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H104" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I104" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105">
@@ -3592,7 +3634,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3601,13 +3643,13 @@
         <v>10</v>
       </c>
       <c r="G105" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H105" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I105" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106">
@@ -3618,7 +3660,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -3627,13 +3669,13 @@
         <v>10</v>
       </c>
       <c r="G106" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H106" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I106" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107">
@@ -3644,7 +3686,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3653,25 +3695,25 @@
         <v>10</v>
       </c>
       <c r="G107" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H107" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J107">
         <v>4</v>
       </c>
       <c r="K107" t="s">
-        <v>40</v>
-      </c>
-      <c r="S107" t="s">
         <v>45</v>
       </c>
-      <c r="T107" t="s">
-        <v>44</v>
+      <c r="X107" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="108">
@@ -3682,7 +3724,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -3691,25 +3733,25 @@
         <v>7</v>
       </c>
       <c r="G108" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I108" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J108">
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>49</v>
-      </c>
-      <c r="S108" t="s">
-        <v>41</v>
-      </c>
-      <c r="T108" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="X108" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="109">
@@ -3720,7 +3762,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -3729,25 +3771,25 @@
         <v>5</v>
       </c>
       <c r="G109" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H109" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I109" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109" t="s">
+        <v>54</v>
+      </c>
+      <c r="X109" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y109" t="s">
         <v>49</v>
-      </c>
-      <c r="S109" t="s">
-        <v>45</v>
-      </c>
-      <c r="T109" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="110">
@@ -3758,7 +3800,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -3767,13 +3809,13 @@
         <v>6</v>
       </c>
       <c r="G110" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H110" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I110" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111">
@@ -3784,7 +3826,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3793,13 +3835,13 @@
         <v>10</v>
       </c>
       <c r="G111" t="s">
+        <v>44</v>
+      </c>
+      <c r="H111" t="s">
+        <v>37</v>
+      </c>
+      <c r="I111" t="s">
         <v>39</v>
-      </c>
-      <c r="H111" t="s">
-        <v>32</v>
-      </c>
-      <c r="I111" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="112">
@@ -3810,7 +3852,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -3819,13 +3861,13 @@
         <v>3</v>
       </c>
       <c r="G112" t="s">
+        <v>44</v>
+      </c>
+      <c r="H112" t="s">
+        <v>37</v>
+      </c>
+      <c r="I112" t="s">
         <v>39</v>
-      </c>
-      <c r="H112" t="s">
-        <v>32</v>
-      </c>
-      <c r="I112" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="113">
@@ -3836,7 +3878,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3845,13 +3887,13 @@
         <v>10</v>
       </c>
       <c r="G113" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H113" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I113" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114">
@@ -3862,7 +3904,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -3871,7 +3913,7 @@
         <v>10</v>
       </c>
       <c r="G114" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115">
@@ -3882,7 +3924,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -3891,13 +3933,13 @@
         <v>4</v>
       </c>
       <c r="G115" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H115" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I115" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116">
@@ -3908,7 +3950,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D116">
         <v>2</v>
@@ -3917,13 +3959,13 @@
         <v>4</v>
       </c>
       <c r="G116" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H116" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I116" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117">
@@ -3934,7 +3976,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D117">
         <v>3</v>
@@ -3943,13 +3985,13 @@
         <v>9</v>
       </c>
       <c r="G117" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H117" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I117" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="118">
@@ -3960,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D118">
         <v>4</v>
@@ -3969,13 +4011,13 @@
         <v>9</v>
       </c>
       <c r="G118" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H118" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I118" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119">
@@ -3986,7 +4028,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -3995,16 +4037,16 @@
         <v>14</v>
       </c>
       <c r="G119" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H119" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I119" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K119" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="120">
@@ -4015,7 +4057,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4024,25 +4066,25 @@
         <v>10</v>
       </c>
       <c r="G120" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H120" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I120" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J120">
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>49</v>
-      </c>
-      <c r="S120" t="s">
-        <v>86</v>
-      </c>
-      <c r="T120" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="X120" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="121">
@@ -4053,7 +4095,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -4062,25 +4104,25 @@
         <v>13</v>
       </c>
       <c r="G121" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H121" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I121" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J121">
         <v>5</v>
       </c>
       <c r="K121" t="s">
-        <v>49</v>
-      </c>
-      <c r="S121" t="s">
-        <v>41</v>
-      </c>
-      <c r="T121" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="X121" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
